--- a/Información del empleado.xlsx
+++ b/Información del empleado.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9D990C9-BDCA-7B42-9CDD-E55EA518B3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonna\Downloads\CARPETA PAGINA WEB\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6F4C468-17EE-4DCB-8744-E4EF569D25DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
   <si>
     <t>Adscripción</t>
   </si>
@@ -214,6 +219,9 @@
   </si>
   <si>
     <t>HN7706H</t>
+  </si>
+  <si>
+    <t>HESN780331SG0</t>
   </si>
 </sst>
 </file>
@@ -586,20 +594,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24269F5-A0A2-9148-B554-D9BDF8893B91}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.99609375" customWidth="1"/>
-    <col min="2" max="2" width="30.265625" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="9.4140625" customWidth="1"/>
-    <col min="5" max="5" width="16.8125" customWidth="1"/>
-    <col min="6" max="6" width="15.87109375" customWidth="1"/>
-    <col min="7" max="7" width="19.1015625" customWidth="1"/>
-    <col min="8" max="9" width="12.375" customWidth="1"/>
-    <col min="10" max="10" width="11.8359375" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" customWidth="1"/>
+    <col min="8" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +639,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -663,7 +671,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -695,7 +703,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -727,7 +735,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -759,7 +767,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -791,7 +799,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -814,7 +822,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -837,7 +845,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -860,7 +868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -876,8 +884,14 @@
       <c r="E10">
         <v>442</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -900,7 +914,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -923,7 +937,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -946,7 +960,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -963,7 +977,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
